--- a/HOMOLOGACION.xlsx
+++ b/HOMOLOGACION.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://agsvsai-my.sharepoint.com/personal/samuel_belmar_nemochile_cl/Documents/Escritorio/PROYECTOS/INGRESO OC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_F25DC773A252ABDACC1048CA911A77FC5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EA01465-F0C0-4815-B4F0-2172240544B0}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="11_F25DC773A252ABDACC1048CA911A77FC5BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADF90C82-84C0-4AF6-AC0E-9D5AC942AD70}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,9 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
   </externalReferences>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$J$240</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1229" uniqueCount="430">
   <si>
     <t>ID</t>
   </si>
@@ -1326,6 +1329,9 @@
   </si>
   <si>
     <t>GUANTE NITRILO NEMOCARE EXAMINACIÓN-PROCEDIMIENTO S/POLVO TALLA M CAJA 100 UNIDADES</t>
+  </si>
+  <si>
+    <t>DET00002</t>
   </si>
 </sst>
 </file>
@@ -1445,11 +1451,11 @@
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="42" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" readingOrder="1"/>
     </xf>
@@ -8137,13 +8143,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J240"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="9" max="9" width="11.44140625" customWidth="1"/>
+    <col min="9" max="9" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -8175,7 +8182,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>2228579</v>
       </c>
@@ -8209,7 +8216,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2228578</v>
       </c>
@@ -8243,7 +8250,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2232148</v>
       </c>
@@ -8277,7 +8284,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>2231181</v>
       </c>
@@ -8311,7 +8318,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>2231178</v>
       </c>
@@ -8345,7 +8352,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>2233076</v>
       </c>
@@ -8378,7 +8385,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2230914</v>
       </c>
@@ -8412,7 +8419,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2233874</v>
       </c>
@@ -8446,7 +8453,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2233873</v>
       </c>
@@ -8480,7 +8487,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2231179</v>
       </c>
@@ -8514,7 +8521,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2231182</v>
       </c>
@@ -8547,7 +8554,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>2230915</v>
       </c>
@@ -8581,7 +8588,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2233876</v>
       </c>
@@ -8615,7 +8622,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2229976</v>
       </c>
@@ -8649,7 +8656,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2229915</v>
       </c>
@@ -8683,7 +8690,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2228580</v>
       </c>
@@ -8717,7 +8724,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2229916</v>
       </c>
@@ -8751,7 +8758,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2233875</v>
       </c>
@@ -8785,7 +8792,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>2230916</v>
       </c>
@@ -8819,7 +8826,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>2233868</v>
       </c>
@@ -8853,7 +8860,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>2230980</v>
       </c>
@@ -8887,7 +8894,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>2230981</v>
       </c>
@@ -8921,7 +8928,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>2229975</v>
       </c>
@@ -8955,7 +8962,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>2234417</v>
       </c>
@@ -8989,7 +8996,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>2233869</v>
       </c>
@@ -9023,7 +9030,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>2230913</v>
       </c>
@@ -9057,7 +9064,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>2233075</v>
       </c>
@@ -9090,7 +9097,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>2233077</v>
       </c>
@@ -9123,7 +9130,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>2232542</v>
       </c>
@@ -9157,7 +9164,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>2232540</v>
       </c>
@@ -9191,7 +9198,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>2230917</v>
       </c>
@@ -9225,7 +9232,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>2231919</v>
       </c>
@@ -9259,7 +9266,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>2232359</v>
       </c>
@@ -9293,7 +9300,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>2228908</v>
       </c>
@@ -9327,7 +9334,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>2232363</v>
       </c>
@@ -9361,7 +9368,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>2232342</v>
       </c>
@@ -9395,7 +9402,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>2232351</v>
       </c>
@@ -9429,7 +9436,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>2232352</v>
       </c>
@@ -9463,7 +9470,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>2232362</v>
       </c>
@@ -9497,7 +9504,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>2232365</v>
       </c>
@@ -9531,7 +9538,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>2232366</v>
       </c>
@@ -9565,7 +9572,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>2232357</v>
       </c>
@@ -9599,7 +9606,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>2232358</v>
       </c>
@@ -9633,7 +9640,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>2232355</v>
       </c>
@@ -9667,7 +9674,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>2232340</v>
       </c>
@@ -9701,7 +9708,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>2232354</v>
       </c>
@@ -9735,7 +9742,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>2232356</v>
       </c>
@@ -9769,7 +9776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>2232347</v>
       </c>
@@ -9803,7 +9810,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>2232341</v>
       </c>
@@ -9837,7 +9844,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>2232364</v>
       </c>
@@ -9871,7 +9878,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
         <v>2234307</v>
       </c>
@@ -9905,7 +9912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>2231916</v>
       </c>
@@ -9939,7 +9946,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>2232345</v>
       </c>
@@ -9973,7 +9980,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>2232346</v>
       </c>
@@ -10007,7 +10014,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>2232353</v>
       </c>
@@ -10041,7 +10048,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>2232361</v>
       </c>
@@ -10075,7 +10082,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>2232360</v>
       </c>
@@ -10109,7 +10116,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>2230647</v>
       </c>
@@ -10143,7 +10150,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>2230649</v>
       </c>
@@ -10177,7 +10184,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>2230648</v>
       </c>
@@ -10211,7 +10218,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>2230567</v>
       </c>
@@ -10245,7 +10252,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>2230644</v>
       </c>
@@ -10279,7 +10286,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
         <v>2231917</v>
       </c>
@@ -10313,7 +10320,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
         <v>2231918</v>
       </c>
@@ -10347,7 +10354,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
         <v>2232538</v>
       </c>
@@ -10381,7 +10388,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
         <v>2230254</v>
       </c>
@@ -10415,7 +10422,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
         <v>2230652</v>
       </c>
@@ -10449,7 +10456,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
         <v>2230646</v>
       </c>
@@ -10483,7 +10490,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
         <v>2230252</v>
       </c>
@@ -10517,7 +10524,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>2234308</v>
       </c>
@@ -10551,7 +10558,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>2230253</v>
       </c>
@@ -10585,7 +10592,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
         <v>2232350</v>
       </c>
@@ -10619,7 +10626,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
         <v>2230651</v>
       </c>
@@ -10653,7 +10660,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
         <v>2230255</v>
       </c>
@@ -10687,7 +10694,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
         <v>2230257</v>
       </c>
@@ -10721,7 +10728,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
         <v>2230653</v>
       </c>
@@ -10755,7 +10762,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
         <v>2230251</v>
       </c>
@@ -10789,7 +10796,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
         <v>2232349</v>
       </c>
@@ -10823,7 +10830,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
         <v>2234305</v>
       </c>
@@ -10857,7 +10864,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
         <v>2232348</v>
       </c>
@@ -10891,7 +10898,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
         <v>2230650</v>
       </c>
@@ -10925,7 +10932,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
         <v>2230256</v>
       </c>
@@ -10959,7 +10966,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="13">
         <v>2230911</v>
       </c>
@@ -10993,7 +11000,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
         <v>2234306</v>
       </c>
@@ -11027,7 +11034,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
         <v>2230645</v>
       </c>
@@ -11061,7 +11068,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
         <v>2232900</v>
       </c>
@@ -11095,7 +11102,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
         <v>2232901</v>
       </c>
@@ -11129,7 +11136,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
         <v>2228387</v>
       </c>
@@ -11163,7 +11170,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
         <v>2228388</v>
       </c>
@@ -11197,7 +11204,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
         <v>2228402</v>
       </c>
@@ -11231,7 +11238,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
         <v>2228401</v>
       </c>
@@ -11265,7 +11272,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="13">
         <v>2228907</v>
       </c>
@@ -11299,7 +11306,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
         <v>2230499</v>
       </c>
@@ -11333,7 +11340,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
         <v>2234412</v>
       </c>
@@ -11367,7 +11374,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
         <v>2232339</v>
       </c>
@@ -11401,7 +11408,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
         <v>2228391</v>
       </c>
@@ -11435,7 +11442,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
         <v>2228398</v>
       </c>
@@ -11469,7 +11476,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
         <v>2232338</v>
       </c>
@@ -11503,7 +11510,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
         <v>2232337</v>
       </c>
@@ -11537,7 +11544,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
         <v>2228389</v>
       </c>
@@ -11571,7 +11578,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
         <v>2232539</v>
       </c>
@@ -11605,7 +11612,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
         <v>2228275</v>
       </c>
@@ -11639,7 +11646,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
         <v>2228390</v>
       </c>
@@ -11673,7 +11680,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
         <v>2228270</v>
       </c>
@@ -11707,7 +11714,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="13">
         <v>2228906</v>
       </c>
@@ -11741,7 +11748,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
         <v>2228276</v>
       </c>
@@ -11775,7 +11782,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
         <v>2228274</v>
       </c>
@@ -11809,7 +11816,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
         <v>2228273</v>
       </c>
@@ -11843,7 +11850,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
         <v>2228405</v>
       </c>
@@ -11877,7 +11884,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
         <v>2230498</v>
       </c>
@@ -11911,7 +11918,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
         <v>2232541</v>
       </c>
@@ -11945,7 +11952,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
         <v>2232537</v>
       </c>
@@ -11979,7 +11986,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
         <v>2228406</v>
       </c>
@@ -12013,7 +12020,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
         <v>2232344</v>
       </c>
@@ -12047,7 +12054,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
         <v>2234413</v>
       </c>
@@ -12081,7 +12088,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
         <v>2229491</v>
       </c>
@@ -12115,7 +12122,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
         <v>2228404</v>
       </c>
@@ -12149,7 +12156,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
         <v>2229065</v>
       </c>
@@ -12183,7 +12190,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
         <v>2228403</v>
       </c>
@@ -12217,7 +12224,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
         <v>2234268</v>
       </c>
@@ -12251,7 +12258,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
         <v>2229066</v>
       </c>
@@ -12285,7 +12292,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
         <v>2233870</v>
       </c>
@@ -12319,7 +12326,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
         <v>2228277</v>
       </c>
@@ -12353,7 +12360,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
         <v>2228271</v>
       </c>
@@ -12387,7 +12394,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
         <v>2228268</v>
       </c>
@@ -12421,7 +12428,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
         <v>2233872</v>
       </c>
@@ -12455,7 +12462,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
         <v>2228272</v>
       </c>
@@ -12489,7 +12496,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
         <v>2229545</v>
       </c>
@@ -12523,7 +12530,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
         <v>2228399</v>
       </c>
@@ -12557,7 +12564,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
         <v>2233871</v>
       </c>
@@ -12591,7 +12598,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
         <v>2228397</v>
       </c>
@@ -12625,7 +12632,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
         <v>2230568</v>
       </c>
@@ -12659,7 +12666,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="15">
         <v>2229547</v>
       </c>
@@ -12693,7 +12700,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
         <v>2228269</v>
       </c>
@@ -12727,7 +12734,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
         <v>2228395</v>
       </c>
@@ -12761,7 +12768,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
         <v>2229059</v>
       </c>
@@ -12795,7 +12802,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
         <v>2228407</v>
       </c>
@@ -12829,7 +12836,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
         <v>2228394</v>
       </c>
@@ -12863,7 +12870,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
         <v>2228392</v>
       </c>
@@ -12897,7 +12904,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
         <v>2228396</v>
       </c>
@@ -12931,7 +12938,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
         <v>2229058</v>
       </c>
@@ -12965,7 +12972,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="13">
         <v>2230912</v>
       </c>
@@ -12999,7 +13006,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
         <v>2228393</v>
       </c>
@@ -13033,7 +13040,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
         <v>2229548</v>
       </c>
@@ -13067,7 +13074,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
         <v>2229543</v>
       </c>
@@ -13101,7 +13108,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
         <v>2228386</v>
       </c>
@@ -13135,7 +13142,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="15">
         <v>2229546</v>
       </c>
@@ -13169,7 +13176,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
         <v>2231797</v>
       </c>
@@ -13203,7 +13210,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
         <v>2231792</v>
       </c>
@@ -13237,7 +13244,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
         <v>2229061</v>
       </c>
@@ -13271,7 +13278,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
         <v>2229062</v>
       </c>
@@ -13305,7 +13312,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
         <v>2231796</v>
       </c>
@@ -13339,7 +13346,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
         <v>2228266</v>
       </c>
@@ -13373,7 +13380,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>2228490</v>
       </c>
@@ -13407,7 +13414,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>2228491</v>
       </c>
@@ -13441,7 +13448,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>2228400</v>
       </c>
@@ -13475,7 +13482,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>2234419</v>
       </c>
@@ -13509,7 +13516,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>2234411</v>
       </c>
@@ -13543,7 +13550,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>2234420</v>
       </c>
@@ -13577,7 +13584,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>2228408</v>
       </c>
@@ -13611,7 +13618,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>2234418</v>
       </c>
@@ -13645,7 +13652,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>2232343</v>
       </c>
@@ -13679,7 +13686,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>2234415</v>
       </c>
@@ -13713,7 +13720,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>2234414</v>
       </c>
@@ -13747,7 +13754,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>2228267</v>
       </c>
@@ -13781,7 +13788,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
         <v>2229549</v>
       </c>
@@ -13815,7 +13822,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
         <v>2236838</v>
       </c>
@@ -13848,7 +13855,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
         <v>2236839</v>
       </c>
@@ -13881,7 +13888,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
         <v>2228663</v>
       </c>
@@ -13915,7 +13922,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
         <v>2228664</v>
       </c>
@@ -13949,7 +13956,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
         <v>2236837</v>
       </c>
@@ -13982,7 +13989,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
         <v>2228665</v>
       </c>
@@ -14016,7 +14023,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
         <v>2228662</v>
       </c>
@@ -14050,7 +14057,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
         <v>2236836</v>
       </c>
@@ -14083,7 +14090,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
         <v>2231560</v>
       </c>
@@ -14117,7 +14124,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
         <v>2229973</v>
       </c>
@@ -14151,7 +14158,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
         <v>2229911</v>
       </c>
@@ -14185,7 +14192,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
         <v>2229060</v>
       </c>
@@ -14218,7 +14225,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
         <v>2231793</v>
       </c>
@@ -14252,7 +14259,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
         <v>2231794</v>
       </c>
@@ -14286,7 +14293,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>2236967</v>
       </c>
@@ -14319,7 +14326,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>2229064</v>
       </c>
@@ -14353,7 +14360,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>2231562</v>
       </c>
@@ -14387,7 +14394,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>2228488</v>
       </c>
@@ -14421,7 +14428,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>2228489</v>
       </c>
@@ -14455,7 +14462,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
         <v>2231558</v>
       </c>
@@ -14489,7 +14496,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
         <v>2231795</v>
       </c>
@@ -14523,7 +14530,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
         <v>2231561</v>
       </c>
@@ -14557,7 +14564,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
         <v>2229068</v>
       </c>
@@ -14591,7 +14598,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
         <v>2229025</v>
       </c>
@@ -14625,7 +14632,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
         <v>2231559</v>
       </c>
@@ -14659,7 +14666,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
         <v>2236925</v>
       </c>
@@ -14692,7 +14699,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
         <v>2229974</v>
       </c>
@@ -14719,14 +14726,14 @@
         <v>1</v>
       </c>
       <c r="I194" s="9">
-        <f t="shared" ref="I194:I240" si="3">G194/H194</f>
+        <f t="shared" ref="I194:I239" si="3">G194/H194</f>
         <v>3064</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
         <v>2229912</v>
       </c>
@@ -14760,7 +14767,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
         <v>2229914</v>
       </c>
@@ -14794,7 +14801,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
         <v>2229913</v>
       </c>
@@ -14828,7 +14835,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
         <v>2229396</v>
       </c>
@@ -14861,7 +14868,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
         <v>2236840</v>
       </c>
@@ -14894,7 +14901,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
         <v>2229026</v>
       </c>
@@ -14928,7 +14935,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
         <v>2229027</v>
       </c>
@@ -14962,7 +14969,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
         <v>2228577</v>
       </c>
@@ -14996,7 +15003,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
         <v>2229067</v>
       </c>
@@ -15030,7 +15037,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
         <v>2229030</v>
       </c>
@@ -15064,7 +15071,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
         <v>2229239</v>
       </c>
@@ -15098,7 +15105,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
         <v>2229233</v>
       </c>
@@ -15132,7 +15139,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
         <v>2229240</v>
       </c>
@@ -15166,7 +15173,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
         <v>2229063</v>
       </c>
@@ -15199,7 +15206,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
         <v>2229227</v>
       </c>
@@ -15233,7 +15240,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
         <v>2228493</v>
       </c>
@@ -15267,7 +15274,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
         <v>2228492</v>
       </c>
@@ -15301,7 +15308,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
         <v>2232755</v>
       </c>
@@ -15335,7 +15342,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
         <v>2234421</v>
       </c>
@@ -15369,7 +15376,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
         <v>2230370</v>
       </c>
@@ -15382,9 +15389,8 @@
       <c r="D214" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E214" s="3" t="str">
-        <f>_xlfn.XLOOKUP(D214,[1]MAESTRA!D:D,[1]MAESTRA!A:A,"")</f>
-        <v>DET00001</v>
+      <c r="E214" s="3" t="s">
+        <v>429</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>384</v>
@@ -15403,7 +15409,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
         <v>2234416</v>
       </c>
@@ -15437,7 +15443,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
         <v>2229232</v>
       </c>
@@ -15471,7 +15477,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
         <v>2232754</v>
       </c>
@@ -15505,7 +15511,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
         <v>2229544</v>
       </c>
@@ -15539,7 +15545,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
         <v>2229234</v>
       </c>
@@ -15573,7 +15579,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
         <v>2231880</v>
       </c>
@@ -15606,7 +15612,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
         <v>2236863</v>
       </c>
@@ -15640,7 +15646,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
         <v>2229228</v>
       </c>
@@ -15674,7 +15680,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
         <v>2230369</v>
       </c>
@@ -15687,9 +15693,8 @@
       <c r="D223" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E223" s="3" t="str">
-        <f>_xlfn.XLOOKUP(D223,[1]MAESTRA!D:D,[1]MAESTRA!A:A,"")</f>
-        <v>DET00001</v>
+      <c r="E223" s="3" t="s">
+        <v>429</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>401</v>
@@ -15708,7 +15713,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
         <v>2234321</v>
       </c>
@@ -15742,7 +15747,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
         <v>2230308</v>
       </c>
@@ -15755,9 +15760,8 @@
       <c r="D225" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E225" s="3" t="str">
-        <f>_xlfn.XLOOKUP(D225,[1]MAESTRA!D:D,[1]MAESTRA!A:A,"")</f>
-        <v>DET00001</v>
+      <c r="E225" s="3" t="s">
+        <v>429</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>406</v>
@@ -15776,7 +15780,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
         <v>2230367</v>
       </c>
@@ -15789,9 +15793,8 @@
       <c r="D226" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E226" s="3" t="str">
-        <f>_xlfn.XLOOKUP(D226,[1]MAESTRA!D:D,[1]MAESTRA!A:A,"")</f>
-        <v>DET00001</v>
+      <c r="E226" s="3" t="s">
+        <v>429</v>
       </c>
       <c r="F226" s="2" t="s">
         <v>407</v>
@@ -15810,7 +15813,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
         <v>2230368</v>
       </c>
@@ -15823,9 +15826,8 @@
       <c r="D227" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E227" s="3" t="str">
-        <f>_xlfn.XLOOKUP(D227,[1]MAESTRA!D:D,[1]MAESTRA!A:A,"")</f>
-        <v>DET00001</v>
+      <c r="E227" s="3" t="s">
+        <v>429</v>
       </c>
       <c r="F227" s="2" t="s">
         <v>408</v>
@@ -15844,7 +15846,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
         <v>2230310</v>
       </c>
@@ -15857,9 +15859,8 @@
       <c r="D228" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E228" s="3" t="str">
-        <f>_xlfn.XLOOKUP(D228,[1]MAESTRA!D:D,[1]MAESTRA!A:A,"")</f>
-        <v>DET00001</v>
+      <c r="E228" s="3" t="s">
+        <v>429</v>
       </c>
       <c r="F228" s="2" t="s">
         <v>409</v>
@@ -15878,7 +15879,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
         <v>2230371</v>
       </c>
@@ -15891,9 +15892,8 @@
       <c r="D229" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E229" s="3" t="str">
-        <f>_xlfn.XLOOKUP(D229,[1]MAESTRA!D:D,[1]MAESTRA!A:A,"")</f>
-        <v>DET00001</v>
+      <c r="E229" s="3" t="s">
+        <v>429</v>
       </c>
       <c r="F229" s="2" t="s">
         <v>410</v>
@@ -15912,7 +15912,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
         <v>2230372</v>
       </c>
@@ -15925,9 +15925,8 @@
       <c r="D230" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E230" s="3" t="str">
-        <f>_xlfn.XLOOKUP(D230,[1]MAESTRA!D:D,[1]MAESTRA!A:A,"")</f>
-        <v>DET00001</v>
+      <c r="E230" s="3" t="s">
+        <v>429</v>
       </c>
       <c r="F230" s="2" t="s">
         <v>411</v>
@@ -15946,7 +15945,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
         <v>2230309</v>
       </c>
@@ -15959,9 +15958,8 @@
       <c r="D231" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E231" s="3" t="str">
-        <f>_xlfn.XLOOKUP(D231,[1]MAESTRA!D:D,[1]MAESTRA!A:A,"")</f>
-        <v>DET00001</v>
+      <c r="E231" s="3" t="s">
+        <v>429</v>
       </c>
       <c r="F231" s="2" t="s">
         <v>401</v>
@@ -15980,7 +15978,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
         <v>2229229</v>
       </c>
@@ -16014,7 +16012,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
         <v>2229235</v>
       </c>
@@ -16048,7 +16046,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
         <v>2229550</v>
       </c>
@@ -16082,7 +16080,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
         <v>2229230</v>
       </c>
@@ -16116,7 +16114,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
         <v>2229236</v>
       </c>
@@ -16150,7 +16148,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
         <v>2229231</v>
       </c>
@@ -16184,7 +16182,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
         <v>2229237</v>
       </c>
@@ -16218,7 +16216,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
         <v>2229238</v>
       </c>
@@ -16252,7 +16250,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
         <v>2231180</v>
       </c>
@@ -16287,11 +16285,18 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:J240" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="DET00001"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A1:A239">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A240">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A239">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
